--- a/sensitivity_results/legacy/multiconcept/experiment_results_grouped_patchedout.xlsx
+++ b/sensitivity_results/legacy/multiconcept/experiment_results_grouped_patchedout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F84AA7D-0584-46EA-9939-7F420BC1ACE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4CD868-0792-42B9-8008-C32F4CCE8884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inception_v3_deer" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="vgg16_deer" sheetId="13" r:id="rId13"/>
     <sheet name="vgg16_horse" sheetId="14" r:id="rId14"/>
     <sheet name="vgg16_zebra" sheetId="15" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">inception_v3_horse!$A$1:$R$48</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5869" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="34">
   <si>
     <t>Precision</t>
   </si>
@@ -157,6 +158,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Deer with Horse background</t>
+  </si>
+  <si>
+    <t>Deer with Zebra background</t>
   </si>
 </sst>
 </file>
@@ -273,12 +280,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -288,7 +295,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -299,13 +306,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -344,6 +347,275 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>353070</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>429</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6071D6C-9E26-1250-0660-2FCAFEE5FBE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="4620270" cy="3077004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>79609</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84BE8017-4E54-B38E-1A10-79A650D1A7A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6096000" y="0"/>
+          <a:ext cx="5086350" cy="3337159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>438977</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>105270</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CB868CD-58C3-51D6-6826-625834B8FCA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12192000" y="180975"/>
+          <a:ext cx="5925377" cy="3543795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>101216</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46A217D9-0502-6DA1-74E7-AF00CA4A8078}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4705350"/>
+          <a:ext cx="5172075" cy="3539741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>200393</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>114670</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054C5DA7-FEFF-5EB6-2C65-8FD2961AF9EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6096000" y="4705350"/>
+          <a:ext cx="2638793" cy="2648320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>371952</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C396483-14D8-9C52-A1F4-A9521AE11EAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9753600" y="4705350"/>
+          <a:ext cx="3419952" cy="3439005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -910,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" ref="P5:P49" si="0">(D5-G5)/D5*100</f>
+        <f t="shared" ref="P5" si="0">(D5-G5)/D5*100</f>
         <v>1.402805611222445</v>
       </c>
       <c r="Q5" s="3" t="s">
@@ -970,7 +1242,7 @@
         <v>31</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" ref="Q6:Q49" si="1">(D6-H6)/D6*100</f>
+        <f t="shared" ref="Q6" si="1">(D6-H6)/D6*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R6" s="3" t="s">
@@ -1030,7 +1302,7 @@
         <v>31</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" ref="R7:R49" si="2">(D7-I7)/D7*100</f>
+        <f t="shared" ref="R7" si="2">(D7-I7)/D7*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1081,7 +1353,7 @@
         <v>23</v>
       </c>
       <c r="P8" s="5">
-        <f t="shared" ref="P8:P49" si="3">(D8-G8)/D8*100</f>
+        <f t="shared" ref="P8" si="3">(D8-G8)/D8*100</f>
         <v>41.482965931863731</v>
       </c>
       <c r="Q8" s="5" t="s">
@@ -1141,7 +1413,7 @@
         <v>31</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" ref="Q9:Q49" si="4">(D9-H9)/D9*100</f>
+        <f t="shared" ref="Q9" si="4">(D9-H9)/D9*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R9" s="3" t="s">
@@ -1201,7 +1473,7 @@
         <v>31</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" ref="R10:R49" si="5">(D10-I10)/D10*100</f>
+        <f t="shared" ref="R10" si="5">(D10-I10)/D10*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1252,7 +1524,7 @@
         <v>22</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" ref="P11:P49" si="6">(D11-G11)/D11*100</f>
+        <f t="shared" ref="P11" si="6">(D11-G11)/D11*100</f>
         <v>3.4042553191489362</v>
       </c>
       <c r="Q11" s="3" t="s">
@@ -1312,7 +1584,7 @@
         <v>31</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" ref="Q12:Q49" si="7">(D12-H12)/D12*100</f>
+        <f t="shared" ref="Q12" si="7">(D12-H12)/D12*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R12" s="3" t="s">
@@ -1372,7 +1644,7 @@
         <v>31</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" ref="R13:R49" si="8">(D13-I13)/D13*100</f>
+        <f t="shared" ref="R13" si="8">(D13-I13)/D13*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1423,7 +1695,7 @@
         <v>23</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" ref="P14:P49" si="9">(D14-G14)/D14*100</f>
+        <f t="shared" ref="P14" si="9">(D14-G14)/D14*100</f>
         <v>6.0120240480961922</v>
       </c>
       <c r="Q14" s="3" t="s">
@@ -1483,7 +1755,7 @@
         <v>31</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" ref="Q15:Q49" si="10">(D15-H15)/D15*100</f>
+        <f t="shared" ref="Q15" si="10">(D15-H15)/D15*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R15" s="3" t="s">
@@ -1543,7 +1815,7 @@
         <v>31</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" ref="R16:R49" si="11">(D16-I16)/D16*100</f>
+        <f t="shared" ref="R16" si="11">(D16-I16)/D16*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1594,7 +1866,7 @@
         <v>24</v>
       </c>
       <c r="P17" s="5">
-        <f t="shared" ref="P17:P49" si="12">(D17-G17)/D17*100</f>
+        <f t="shared" ref="P17" si="12">(D17-G17)/D17*100</f>
         <v>18.637274549098194</v>
       </c>
       <c r="Q17" s="5" t="s">
@@ -1654,7 +1926,7 @@
         <v>31</v>
       </c>
       <c r="Q18" s="3">
-        <f t="shared" ref="Q18:Q49" si="13">(D18-H18)/D18*100</f>
+        <f t="shared" ref="Q18" si="13">(D18-H18)/D18*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R18" s="3" t="s">
@@ -1714,7 +1986,7 @@
         <v>31</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" ref="R19:R49" si="14">(D19-I19)/D19*100</f>
+        <f t="shared" ref="R19" si="14">(D19-I19)/D19*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1765,7 +2037,7 @@
         <v>24</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" ref="P20:P49" si="15">(D20-G20)/D20*100</f>
+        <f t="shared" ref="P20" si="15">(D20-G20)/D20*100</f>
         <v>2.2044088176352705</v>
       </c>
       <c r="Q20" s="3" t="s">
@@ -1825,7 +2097,7 @@
         <v>31</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" ref="Q21:Q49" si="16">(D21-H21)/D21*100</f>
+        <f t="shared" ref="Q21" si="16">(D21-H21)/D21*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R21" s="3" t="s">
@@ -1885,7 +2157,7 @@
         <v>31</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" ref="R22:R49" si="17">(D22-I22)/D22*100</f>
+        <f t="shared" ref="R22" si="17">(D22-I22)/D22*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -1936,7 +2208,7 @@
         <v>20</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" ref="P23:P49" si="18">(D23-G23)/D23*100</f>
+        <f t="shared" ref="P23" si="18">(D23-G23)/D23*100</f>
         <v>17.434869739478959</v>
       </c>
       <c r="Q23" s="3" t="s">
@@ -1996,7 +2268,7 @@
         <v>31</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" ref="Q24:Q49" si="19">(D24-H24)/D24*100</f>
+        <f t="shared" ref="Q24" si="19">(D24-H24)/D24*100</f>
         <v>0.71022727272727271</v>
       </c>
       <c r="R24" s="3" t="s">
@@ -2056,7 +2328,7 @@
         <v>31</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" ref="R25:R49" si="20">(D25-I25)/D25*100</f>
+        <f t="shared" ref="R25" si="20">(D25-I25)/D25*100</f>
         <v>0.42613636363636359</v>
       </c>
     </row>
@@ -2107,7 +2379,7 @@
         <v>22</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" ref="P26:P49" si="21">(D26-G26)/D26*100</f>
+        <f t="shared" ref="P26" si="21">(D26-G26)/D26*100</f>
         <v>0.77519379844961245</v>
       </c>
       <c r="Q26" s="3" t="s">
@@ -2167,7 +2439,7 @@
         <v>31</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" ref="Q27:Q49" si="22">(D27-H27)/D27*100</f>
+        <f t="shared" ref="Q27" si="22">(D27-H27)/D27*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R27" s="3" t="s">
@@ -2227,7 +2499,7 @@
         <v>31</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" ref="R28:R49" si="23">(D28-I28)/D28*100</f>
+        <f t="shared" ref="R28" si="23">(D28-I28)/D28*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -2278,7 +2550,7 @@
         <v>23</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" ref="P29:P49" si="24">(D29-G29)/D29*100</f>
+        <f t="shared" ref="P29" si="24">(D29-G29)/D29*100</f>
         <v>41.085271317829459</v>
       </c>
       <c r="Q29" s="5" t="s">
@@ -2338,7 +2610,7 @@
         <v>31</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ref="Q30:Q49" si="25">(D30-H30)/D30*100</f>
+        <f t="shared" ref="Q30" si="25">(D30-H30)/D30*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R30" s="3" t="s">
@@ -2398,7 +2670,7 @@
         <v>31</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31:R49" si="26">(D31-I31)/D31*100</f>
+        <f t="shared" ref="R31" si="26">(D31-I31)/D31*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -2449,7 +2721,7 @@
         <v>22</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" ref="P32:P49" si="27">(D32-G32)/D32*100</f>
+        <f t="shared" ref="P32" si="27">(D32-G32)/D32*100</f>
         <v>1.1627906976744187</v>
       </c>
       <c r="Q32" s="3" t="s">
@@ -2509,7 +2781,7 @@
         <v>31</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:Q49" si="28">(D33-H33)/D33*100</f>
+        <f t="shared" ref="Q33" si="28">(D33-H33)/D33*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R33" s="3" t="s">
@@ -2569,7 +2841,7 @@
         <v>31</v>
       </c>
       <c r="R34" s="3">
-        <f t="shared" ref="R34:R49" si="29">(D34-I34)/D34*100</f>
+        <f t="shared" ref="R34" si="29">(D34-I34)/D34*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -2620,7 +2892,7 @@
         <v>24</v>
       </c>
       <c r="P35" s="5">
-        <f t="shared" ref="P35:P49" si="30">(D35-G35)/D35*100</f>
+        <f t="shared" ref="P35" si="30">(D35-G35)/D35*100</f>
         <v>21.705426356589147</v>
       </c>
       <c r="Q35" s="5" t="s">
@@ -2680,7 +2952,7 @@
         <v>31</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" ref="Q36:Q49" si="31">(D36-H36)/D36*100</f>
+        <f t="shared" ref="Q36" si="31">(D36-H36)/D36*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R36" s="3" t="s">
@@ -2740,7 +3012,7 @@
         <v>31</v>
       </c>
       <c r="R37" s="3">
-        <f t="shared" ref="R37:R49" si="32">(D37-I37)/D37*100</f>
+        <f t="shared" ref="R37" si="32">(D37-I37)/D37*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -2791,7 +3063,7 @@
         <v>24</v>
       </c>
       <c r="P38" s="3">
-        <f t="shared" ref="P38:P49" si="33">(D38-G38)/D38*100</f>
+        <f t="shared" ref="P38" si="33">(D38-G38)/D38*100</f>
         <v>0.77519379844961245</v>
       </c>
       <c r="Q38" s="3" t="s">
@@ -2851,7 +3123,7 @@
         <v>31</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" ref="Q39:Q49" si="34">(D39-H39)/D39*100</f>
+        <f t="shared" ref="Q39" si="34">(D39-H39)/D39*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R39" s="3" t="s">
@@ -2911,7 +3183,7 @@
         <v>31</v>
       </c>
       <c r="R40" s="3">
-        <f t="shared" ref="R40:R49" si="35">(D40-I40)/D40*100</f>
+        <f t="shared" ref="R40" si="35">(D40-I40)/D40*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -2962,7 +3234,7 @@
         <v>23</v>
       </c>
       <c r="P41" s="3">
-        <f t="shared" ref="P41:P49" si="36">(D41-G41)/D41*100</f>
+        <f t="shared" ref="P41" si="36">(D41-G41)/D41*100</f>
         <v>3.8759689922480618</v>
       </c>
       <c r="Q41" s="3" t="s">
@@ -3022,7 +3294,7 @@
         <v>31</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" ref="Q42:Q49" si="37">(D42-H42)/D42*100</f>
+        <f t="shared" ref="Q42" si="37">(D42-H42)/D42*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R42" s="3" t="s">
@@ -3082,7 +3354,7 @@
         <v>31</v>
       </c>
       <c r="R43" s="3">
-        <f t="shared" ref="R43:R49" si="38">(D43-I43)/D43*100</f>
+        <f t="shared" ref="R43" si="38">(D43-I43)/D43*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -3133,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="P44" s="3">
-        <f t="shared" ref="P44:P49" si="39">(D44-G44)/D44*100</f>
+        <f t="shared" ref="P44" si="39">(D44-G44)/D44*100</f>
         <v>0.77519379844961245</v>
       </c>
       <c r="Q44" s="3" t="s">
@@ -3193,7 +3465,7 @@
         <v>31</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" ref="Q45:Q49" si="40">(D45-H45)/D45*100</f>
+        <f t="shared" ref="Q45" si="40">(D45-H45)/D45*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R45" s="3" t="s">
@@ -3253,7 +3525,7 @@
         <v>31</v>
       </c>
       <c r="R46" s="3">
-        <f t="shared" ref="R46:R49" si="41">(D46-I46)/D46*100</f>
+        <f t="shared" ref="R46" si="41">(D46-I46)/D46*100</f>
         <v>0.97799511002444983</v>
       </c>
     </row>
@@ -3304,7 +3576,7 @@
         <v>20</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" ref="P47:P49" si="42">(D47-G47)/D47*100</f>
+        <f t="shared" ref="P47" si="42">(D47-G47)/D47*100</f>
         <v>15.503875968992247</v>
       </c>
       <c r="Q47" s="3" t="s">
@@ -3364,7 +3636,7 @@
         <v>31</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" ref="Q48:Q49" si="43">(D48-H48)/D48*100</f>
+        <f t="shared" ref="Q48" si="43">(D48-H48)/D48*100</f>
         <v>1.6260162601626018</v>
       </c>
       <c r="R48" s="3" t="s">
@@ -3722,7 +3994,7 @@
         <v>22</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" ref="P5:P49" si="0">(D5-G5)/D5*100</f>
+        <f t="shared" ref="P5" si="0">(D5-G5)/D5*100</f>
         <v>13.827655310621243</v>
       </c>
       <c r="Q5" s="3" t="s">
@@ -3782,7 +4054,7 @@
         <v>31</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" ref="Q6:Q49" si="1">(D6-H6)/D6*100</f>
+        <f t="shared" ref="Q6" si="1">(D6-H6)/D6*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R6" s="3" t="s">
@@ -3842,7 +4114,7 @@
         <v>31</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" ref="R7:R49" si="2">(D7-I7)/D7*100</f>
+        <f t="shared" ref="R7" si="2">(D7-I7)/D7*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -3893,7 +4165,7 @@
         <v>23</v>
       </c>
       <c r="P8" s="5">
-        <f t="shared" ref="P8:P49" si="3">(D8-G8)/D8*100</f>
+        <f t="shared" ref="P8" si="3">(D8-G8)/D8*100</f>
         <v>32.064128256513023</v>
       </c>
       <c r="Q8" s="5" t="s">
@@ -3953,7 +4225,7 @@
         <v>31</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" ref="Q9:Q49" si="4">(D9-H9)/D9*100</f>
+        <f t="shared" ref="Q9" si="4">(D9-H9)/D9*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R9" s="3" t="s">
@@ -4013,7 +4285,7 @@
         <v>31</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" ref="R10:R49" si="5">(D10-I10)/D10*100</f>
+        <f t="shared" ref="R10" si="5">(D10-I10)/D10*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4064,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" ref="P11:P49" si="6">(D11-G11)/D11*100</f>
+        <f t="shared" ref="P11" si="6">(D11-G11)/D11*100</f>
         <v>27.23404255319149</v>
       </c>
       <c r="Q11" s="3" t="s">
@@ -4124,7 +4396,7 @@
         <v>31</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" ref="Q12:Q49" si="7">(D12-H12)/D12*100</f>
+        <f t="shared" ref="Q12" si="7">(D12-H12)/D12*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R12" s="3" t="s">
@@ -4184,7 +4456,7 @@
         <v>31</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" ref="R13:R49" si="8">(D13-I13)/D13*100</f>
+        <f t="shared" ref="R13" si="8">(D13-I13)/D13*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4235,7 +4507,7 @@
         <v>23</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" ref="P14:P49" si="9">(D14-G14)/D14*100</f>
+        <f t="shared" ref="P14" si="9">(D14-G14)/D14*100</f>
         <v>26.252505010020037</v>
       </c>
       <c r="Q14" s="3" t="s">
@@ -4295,7 +4567,7 @@
         <v>31</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" ref="Q15:Q49" si="10">(D15-H15)/D15*100</f>
+        <f t="shared" ref="Q15" si="10">(D15-H15)/D15*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R15" s="3" t="s">
@@ -4355,7 +4627,7 @@
         <v>31</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" ref="R16:R49" si="11">(D16-I16)/D16*100</f>
+        <f t="shared" ref="R16" si="11">(D16-I16)/D16*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4406,7 +4678,7 @@
         <v>24</v>
       </c>
       <c r="P17" s="5">
-        <f t="shared" ref="P17:P49" si="12">(D17-G17)/D17*100</f>
+        <f t="shared" ref="P17" si="12">(D17-G17)/D17*100</f>
         <v>55.91182364729459</v>
       </c>
       <c r="Q17" s="5" t="s">
@@ -4466,7 +4738,7 @@
         <v>31</v>
       </c>
       <c r="Q18" s="3">
-        <f t="shared" ref="Q18:Q49" si="13">(D18-H18)/D18*100</f>
+        <f t="shared" ref="Q18" si="13">(D18-H18)/D18*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R18" s="3" t="s">
@@ -4526,7 +4798,7 @@
         <v>31</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" ref="R19:R49" si="14">(D19-I19)/D19*100</f>
+        <f t="shared" ref="R19" si="14">(D19-I19)/D19*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4577,7 +4849,7 @@
         <v>24</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" ref="P20:P49" si="15">(D20-G20)/D20*100</f>
+        <f t="shared" ref="P20" si="15">(D20-G20)/D20*100</f>
         <v>17.635270541082164</v>
       </c>
       <c r="Q20" s="3" t="s">
@@ -4637,7 +4909,7 @@
         <v>31</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" ref="Q21:Q49" si="16">(D21-H21)/D21*100</f>
+        <f t="shared" ref="Q21" si="16">(D21-H21)/D21*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R21" s="3" t="s">
@@ -4697,7 +4969,7 @@
         <v>31</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" ref="R22:R49" si="17">(D22-I22)/D22*100</f>
+        <f t="shared" ref="R22" si="17">(D22-I22)/D22*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4748,7 +5020,7 @@
         <v>20</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" ref="P23:P49" si="18">(D23-G23)/D23*100</f>
+        <f t="shared" ref="P23" si="18">(D23-G23)/D23*100</f>
         <v>26.052104208416832</v>
       </c>
       <c r="Q23" s="3" t="s">
@@ -4808,7 +5080,7 @@
         <v>31</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" ref="Q24:Q49" si="19">(D24-H24)/D24*100</f>
+        <f t="shared" ref="Q24" si="19">(D24-H24)/D24*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R24" s="3" t="s">
@@ -4868,7 +5140,7 @@
         <v>31</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" ref="R25:R49" si="20">(D25-I25)/D25*100</f>
+        <f t="shared" ref="R25" si="20">(D25-I25)/D25*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -4919,7 +5191,7 @@
         <v>22</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" ref="P26:P49" si="21">(D26-G26)/D26*100</f>
+        <f t="shared" ref="P26" si="21">(D26-G26)/D26*100</f>
         <v>15.503875968992247</v>
       </c>
       <c r="Q26" s="3" t="s">
@@ -4979,7 +5251,7 @@
         <v>31</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" ref="Q27:Q49" si="22">(D27-H27)/D27*100</f>
+        <f t="shared" ref="Q27" si="22">(D27-H27)/D27*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R27" s="3" t="s">
@@ -5039,7 +5311,7 @@
         <v>31</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" ref="R28:R49" si="23">(D28-I28)/D28*100</f>
+        <f t="shared" ref="R28" si="23">(D28-I28)/D28*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5090,7 +5362,7 @@
         <v>23</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" ref="P29:P49" si="24">(D29-G29)/D29*100</f>
+        <f t="shared" ref="P29" si="24">(D29-G29)/D29*100</f>
         <v>31.782945736434108</v>
       </c>
       <c r="Q29" s="5" t="s">
@@ -5150,7 +5422,7 @@
         <v>31</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ref="Q30:Q49" si="25">(D30-H30)/D30*100</f>
+        <f t="shared" ref="Q30" si="25">(D30-H30)/D30*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R30" s="3" t="s">
@@ -5210,7 +5482,7 @@
         <v>31</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31:R49" si="26">(D31-I31)/D31*100</f>
+        <f t="shared" ref="R31" si="26">(D31-I31)/D31*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5261,7 +5533,7 @@
         <v>22</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" ref="P32:P49" si="27">(D32-G32)/D32*100</f>
+        <f t="shared" ref="P32" si="27">(D32-G32)/D32*100</f>
         <v>22.093023255813954</v>
       </c>
       <c r="Q32" s="3" t="s">
@@ -5321,7 +5593,7 @@
         <v>31</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:Q49" si="28">(D33-H33)/D33*100</f>
+        <f t="shared" ref="Q33" si="28">(D33-H33)/D33*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R33" s="3" t="s">
@@ -5381,7 +5653,7 @@
         <v>31</v>
       </c>
       <c r="R34" s="3">
-        <f t="shared" ref="R34:R49" si="29">(D34-I34)/D34*100</f>
+        <f t="shared" ref="R34" si="29">(D34-I34)/D34*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5432,7 +5704,7 @@
         <v>24</v>
       </c>
       <c r="P35" s="5">
-        <f t="shared" ref="P35:P49" si="30">(D35-G35)/D35*100</f>
+        <f t="shared" ref="P35" si="30">(D35-G35)/D35*100</f>
         <v>53.488372093023251</v>
       </c>
       <c r="Q35" s="5" t="s">
@@ -5492,7 +5764,7 @@
         <v>31</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" ref="Q36:Q49" si="31">(D36-H36)/D36*100</f>
+        <f t="shared" ref="Q36" si="31">(D36-H36)/D36*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R36" s="3" t="s">
@@ -5552,7 +5824,7 @@
         <v>31</v>
       </c>
       <c r="R37" s="3">
-        <f t="shared" ref="R37:R49" si="32">(D37-I37)/D37*100</f>
+        <f t="shared" ref="R37" si="32">(D37-I37)/D37*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5603,7 +5875,7 @@
         <v>24</v>
       </c>
       <c r="P38" s="3">
-        <f t="shared" ref="P38:P49" si="33">(D38-G38)/D38*100</f>
+        <f t="shared" ref="P38" si="33">(D38-G38)/D38*100</f>
         <v>19.379844961240313</v>
       </c>
       <c r="Q38" s="3" t="s">
@@ -5663,7 +5935,7 @@
         <v>31</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" ref="Q39:Q49" si="34">(D39-H39)/D39*100</f>
+        <f t="shared" ref="Q39" si="34">(D39-H39)/D39*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R39" s="3" t="s">
@@ -5723,7 +5995,7 @@
         <v>31</v>
       </c>
       <c r="R40" s="3">
-        <f t="shared" ref="R40:R49" si="35">(D40-I40)/D40*100</f>
+        <f t="shared" ref="R40" si="35">(D40-I40)/D40*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5774,7 +6046,7 @@
         <v>23</v>
       </c>
       <c r="P41" s="3">
-        <f t="shared" ref="P41:P49" si="36">(D41-G41)/D41*100</f>
+        <f t="shared" ref="P41" si="36">(D41-G41)/D41*100</f>
         <v>23.255813953488371</v>
       </c>
       <c r="Q41" s="3" t="s">
@@ -5834,7 +6106,7 @@
         <v>31</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" ref="Q42:Q49" si="37">(D42-H42)/D42*100</f>
+        <f t="shared" ref="Q42" si="37">(D42-H42)/D42*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R42" s="3" t="s">
@@ -5894,7 +6166,7 @@
         <v>31</v>
       </c>
       <c r="R43" s="3">
-        <f t="shared" ref="R43:R49" si="38">(D43-I43)/D43*100</f>
+        <f t="shared" ref="R43" si="38">(D43-I43)/D43*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -5945,7 +6217,7 @@
         <v>20</v>
       </c>
       <c r="P44" s="3">
-        <f t="shared" ref="P44:P49" si="39">(D44-G44)/D44*100</f>
+        <f t="shared" ref="P44" si="39">(D44-G44)/D44*100</f>
         <v>25.581395348837212</v>
       </c>
       <c r="Q44" s="3" t="s">
@@ -6005,7 +6277,7 @@
         <v>31</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" ref="Q45:Q49" si="40">(D45-H45)/D45*100</f>
+        <f t="shared" ref="Q45" si="40">(D45-H45)/D45*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R45" s="3" t="s">
@@ -6065,7 +6337,7 @@
         <v>31</v>
       </c>
       <c r="R46" s="3">
-        <f t="shared" ref="R46:R49" si="41">(D46-I46)/D46*100</f>
+        <f t="shared" ref="R46" si="41">(D46-I46)/D46*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -6116,7 +6388,7 @@
         <v>20</v>
       </c>
       <c r="P47" s="3">
-        <f t="shared" ref="P47:P49" si="42">(D47-G47)/D47*100</f>
+        <f t="shared" ref="P47" si="42">(D47-G47)/D47*100</f>
         <v>21.705426356589147</v>
       </c>
       <c r="Q47" s="3" t="s">
@@ -6176,7 +6448,7 @@
         <v>31</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" ref="Q48:Q49" si="43">(D48-H48)/D48*100</f>
+        <f t="shared" ref="Q48" si="43">(D48-H48)/D48*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R48" s="3" t="s">
@@ -6528,7 +6800,7 @@
         <v>20</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" ref="P5:P49" si="0">(D5-G5)/D5*100</f>
+        <f t="shared" ref="P5" si="0">(D5-G5)/D5*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q5" s="7" t="s">
@@ -6588,7 +6860,7 @@
         <v>31</v>
       </c>
       <c r="Q6" s="7">
-        <f t="shared" ref="Q6:Q49" si="1">(D6-H6)/D6*100</f>
+        <f t="shared" ref="Q6" si="1">(D6-H6)/D6*100</f>
         <v>28.23343848580442</v>
       </c>
       <c r="R6" s="7" t="s">
@@ -6648,7 +6920,7 @@
         <v>31</v>
       </c>
       <c r="R7" s="7">
-        <f t="shared" ref="R7:R49" si="2">(D7-I7)/D7*100</f>
+        <f t="shared" ref="R7" si="2">(D7-I7)/D7*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -6699,7 +6971,7 @@
         <v>22</v>
       </c>
       <c r="P8" s="7">
-        <f t="shared" ref="P8:P49" si="3">(D8-G8)/D8*100</f>
+        <f t="shared" ref="P8" si="3">(D8-G8)/D8*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q8" s="7" t="s">
@@ -6759,7 +7031,7 @@
         <v>31</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" ref="Q9:Q49" si="4">(D9-H9)/D9*100</f>
+        <f t="shared" ref="Q9" si="4">(D9-H9)/D9*100</f>
         <v>21.766561514195583</v>
       </c>
       <c r="R9" s="7" t="s">
@@ -6819,7 +7091,7 @@
         <v>31</v>
       </c>
       <c r="R10" s="7">
-        <f t="shared" ref="R10:R49" si="5">(D10-I10)/D10*100</f>
+        <f t="shared" ref="R10" si="5">(D10-I10)/D10*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -6870,7 +7142,7 @@
         <v>22</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" ref="P11:P49" si="6">(D11-G11)/D11*100</f>
+        <f t="shared" ref="P11" si="6">(D11-G11)/D11*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q11" s="7" t="s">
@@ -6930,7 +7202,7 @@
         <v>31</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" ref="Q12:Q49" si="7">(D12-H12)/D12*100</f>
+        <f t="shared" ref="Q12" si="7">(D12-H12)/D12*100</f>
         <v>43.533123028391167</v>
       </c>
       <c r="R12" s="7" t="s">
@@ -6990,7 +7262,7 @@
         <v>31</v>
       </c>
       <c r="R13" s="7">
-        <f t="shared" ref="R13:R49" si="8">(D13-I13)/D13*100</f>
+        <f t="shared" ref="R13" si="8">(D13-I13)/D13*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -7041,7 +7313,7 @@
         <v>23</v>
       </c>
       <c r="P14" s="7">
-        <f t="shared" ref="P14:P49" si="9">(D14-G14)/D14*100</f>
+        <f t="shared" ref="P14" si="9">(D14-G14)/D14*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q14" s="7" t="s">
@@ -7161,7 +7433,7 @@
         <v>31</v>
       </c>
       <c r="R16" s="7">
-        <f t="shared" ref="R16:R49" si="10">(D16-I16)/D16*100</f>
+        <f t="shared" ref="R16" si="10">(D16-I16)/D16*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -7212,7 +7484,7 @@
         <v>24</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" ref="P17:P49" si="11">(D17-G17)/D17*100</f>
+        <f t="shared" ref="P17" si="11">(D17-G17)/D17*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q17" s="7" t="s">
@@ -7272,7 +7544,7 @@
         <v>31</v>
       </c>
       <c r="Q18" s="5">
-        <f t="shared" ref="Q18:Q49" si="12">(D18-H18)/D18*100</f>
+        <f t="shared" ref="Q18" si="12">(D18-H18)/D18*100</f>
         <v>63.249211356466873</v>
       </c>
       <c r="R18" s="7" t="s">
@@ -7332,7 +7604,7 @@
         <v>31</v>
       </c>
       <c r="R19" s="7">
-        <f t="shared" ref="R19:R49" si="13">(D19-I19)/D19*100</f>
+        <f t="shared" ref="R19" si="13">(D19-I19)/D19*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -7383,7 +7655,7 @@
         <v>24</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" ref="P20:P49" si="14">(D20-G20)/D20*100</f>
+        <f t="shared" ref="P20" si="14">(D20-G20)/D20*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q20" s="7" t="s">
@@ -7443,7 +7715,7 @@
         <v>31</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" ref="Q21:Q49" si="15">(D21-H21)/D21*100</f>
+        <f t="shared" ref="Q21" si="15">(D21-H21)/D21*100</f>
         <v>54.347826086956516</v>
       </c>
       <c r="R21" s="7" t="s">
@@ -7503,7 +7775,7 @@
         <v>31</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:R49" si="16">(D22-I22)/D22*100</f>
+        <f t="shared" ref="R22" si="16">(D22-I22)/D22*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -7554,7 +7826,7 @@
         <v>23</v>
       </c>
       <c r="P23" s="7">
-        <f t="shared" ref="P23:P49" si="17">(D23-G23)/D23*100</f>
+        <f t="shared" ref="P23" si="17">(D23-G23)/D23*100</f>
         <v>4.4034090909090908</v>
       </c>
       <c r="Q23" s="7" t="s">
@@ -7614,7 +7886,7 @@
         <v>31</v>
       </c>
       <c r="Q24" s="5">
-        <f t="shared" ref="Q24:Q49" si="18">(D24-H24)/D24*100</f>
+        <f t="shared" ref="Q24" si="18">(D24-H24)/D24*100</f>
         <v>45.425867507886437</v>
       </c>
       <c r="R24" s="7" t="s">
@@ -7674,7 +7946,7 @@
         <v>31</v>
       </c>
       <c r="R25" s="7">
-        <f t="shared" ref="R25:R49" si="19">(D25-I25)/D25*100</f>
+        <f t="shared" ref="R25" si="19">(D25-I25)/D25*100</f>
         <v>1.5625</v>
       </c>
     </row>
@@ -7725,7 +7997,7 @@
         <v>22</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" ref="P26:P49" si="20">(D26-G26)/D26*100</f>
+        <f t="shared" ref="P26" si="20">(D26-G26)/D26*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q26" s="7" t="s">
@@ -7785,7 +8057,7 @@
         <v>31</v>
       </c>
       <c r="Q27" s="7">
-        <f t="shared" ref="Q27:Q49" si="21">(D27-H27)/D27*100</f>
+        <f t="shared" ref="Q27" si="21">(D27-H27)/D27*100</f>
         <v>29.27927927927928</v>
       </c>
       <c r="R27" s="7" t="s">
@@ -7845,7 +8117,7 @@
         <v>31</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" ref="R28:R49" si="22">(D28-I28)/D28*100</f>
+        <f t="shared" ref="R28" si="22">(D28-I28)/D28*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -7896,7 +8168,7 @@
         <v>23</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" ref="P29:P49" si="23">(D29-G29)/D29*100</f>
+        <f t="shared" ref="P29" si="23">(D29-G29)/D29*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q29" s="7" t="s">
@@ -7956,7 +8228,7 @@
         <v>31</v>
       </c>
       <c r="Q30" s="7">
-        <f t="shared" ref="Q30:Q49" si="24">(D30-H30)/D30*100</f>
+        <f t="shared" ref="Q30" si="24">(D30-H30)/D30*100</f>
         <v>20.72072072072072</v>
       </c>
       <c r="R30" s="7" t="s">
@@ -8016,7 +8288,7 @@
         <v>31</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" ref="R31:R49" si="25">(D31-I31)/D31*100</f>
+        <f t="shared" ref="R31" si="25">(D31-I31)/D31*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8067,7 +8339,7 @@
         <v>20</v>
       </c>
       <c r="P32" s="7">
-        <f t="shared" ref="P32:P49" si="26">(D32-G32)/D32*100</f>
+        <f t="shared" ref="P32" si="26">(D32-G32)/D32*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q32" s="7" t="s">
@@ -8127,7 +8399,7 @@
         <v>31</v>
       </c>
       <c r="Q33" s="7">
-        <f t="shared" ref="Q33:Q49" si="27">(D33-H33)/D33*100</f>
+        <f t="shared" ref="Q33" si="27">(D33-H33)/D33*100</f>
         <v>12.612612612612612</v>
       </c>
       <c r="R33" s="7" t="s">
@@ -8187,7 +8459,7 @@
         <v>31</v>
       </c>
       <c r="R34" s="7">
-        <f t="shared" ref="R34:R49" si="28">(D34-I34)/D34*100</f>
+        <f t="shared" ref="R34" si="28">(D34-I34)/D34*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8238,7 +8510,7 @@
         <v>22</v>
       </c>
       <c r="P35" s="7">
-        <f t="shared" ref="P35:P49" si="29">(D35-G35)/D35*100</f>
+        <f t="shared" ref="P35" si="29">(D35-G35)/D35*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q35" s="7" t="s">
@@ -8298,7 +8570,7 @@
         <v>31</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" ref="Q36:Q49" si="30">(D36-H36)/D36*100</f>
+        <f t="shared" ref="Q36" si="30">(D36-H36)/D36*100</f>
         <v>43.693693693693689</v>
       </c>
       <c r="R36" s="7" t="s">
@@ -8358,7 +8630,7 @@
         <v>31</v>
       </c>
       <c r="R37" s="7">
-        <f t="shared" ref="R37:R49" si="31">(D37-I37)/D37*100</f>
+        <f t="shared" ref="R37" si="31">(D37-I37)/D37*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8409,7 +8681,7 @@
         <v>24</v>
       </c>
       <c r="P38" s="7">
-        <f t="shared" ref="P38:P49" si="32">(D38-G38)/D38*100</f>
+        <f t="shared" ref="P38" si="32">(D38-G38)/D38*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q38" s="7" t="s">
@@ -8469,7 +8741,7 @@
         <v>31</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q39:Q49" si="33">(D39-H39)/D39*100</f>
+        <f t="shared" ref="Q39" si="33">(D39-H39)/D39*100</f>
         <v>58.108108108108105</v>
       </c>
       <c r="R39" s="7" t="s">
@@ -8529,7 +8801,7 @@
         <v>31</v>
       </c>
       <c r="R40" s="7">
-        <f t="shared" ref="R40:R49" si="34">(D40-I40)/D40*100</f>
+        <f t="shared" ref="R40" si="34">(D40-I40)/D40*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8580,7 +8852,7 @@
         <v>24</v>
       </c>
       <c r="P41" s="7">
-        <f t="shared" ref="P41:P49" si="35">(D41-G41)/D41*100</f>
+        <f t="shared" ref="P41" si="35">(D41-G41)/D41*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q41" s="7" t="s">
@@ -8640,7 +8912,7 @@
         <v>31</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" ref="Q42:Q49" si="36">(D42-H42)/D42*100</f>
+        <f t="shared" ref="Q42" si="36">(D42-H42)/D42*100</f>
         <v>56.306306306306311</v>
       </c>
       <c r="R42" s="7" t="s">
@@ -8700,7 +8972,7 @@
         <v>31</v>
       </c>
       <c r="R43" s="7">
-        <f t="shared" ref="R43:R49" si="37">(D43-I43)/D43*100</f>
+        <f t="shared" ref="R43" si="37">(D43-I43)/D43*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8751,7 +9023,7 @@
         <v>20</v>
       </c>
       <c r="P44" s="7">
-        <f t="shared" ref="P44:P49" si="38">(D44-G44)/D44*100</f>
+        <f t="shared" ref="P44" si="38">(D44-G44)/D44*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q44" s="7" t="s">
@@ -8811,7 +9083,7 @@
         <v>31</v>
       </c>
       <c r="Q45" s="7">
-        <f t="shared" ref="Q45:Q49" si="39">(D45-H45)/D45*100</f>
+        <f t="shared" ref="Q45" si="39">(D45-H45)/D45*100</f>
         <v>32.882882882882889</v>
       </c>
       <c r="R45" s="7" t="s">
@@ -8871,7 +9143,7 @@
         <v>31</v>
       </c>
       <c r="R46" s="7">
-        <f t="shared" ref="R46:R49" si="40">(D46-I46)/D46*100</f>
+        <f t="shared" ref="R46" si="40">(D46-I46)/D46*100</f>
         <v>2.9339853300733498</v>
       </c>
     </row>
@@ -8922,7 +9194,7 @@
         <v>23</v>
       </c>
       <c r="P47" s="7">
-        <f t="shared" ref="P47:P49" si="41">(D47-G47)/D47*100</f>
+        <f t="shared" ref="P47" si="41">(D47-G47)/D47*100</f>
         <v>4.5197740112994351</v>
       </c>
       <c r="Q47" s="7" t="s">
@@ -8982,7 +9254,7 @@
         <v>31</v>
       </c>
       <c r="Q48" s="5">
-        <f t="shared" ref="Q48:Q49" si="42">(D48-H48)/D48*100</f>
+        <f t="shared" ref="Q48" si="42">(D48-H48)/D48*100</f>
         <v>46.846846846846844</v>
       </c>
       <c r="R48" s="7" t="s">
@@ -9060,8 +9332,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
@@ -9113,7 +9384,7 @@
       <c r="P1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="11"/>
+      <c r="Q1" s="3"/>
       <c r="R1" s="7"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -9166,7 +9437,7 @@
         <f>(D2-G2)/D2*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R2" s="7" t="s">
@@ -9222,7 +9493,7 @@
       <c r="P3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="3">
         <f>(D3-H3)/D3*100</f>
         <v>3.2670454545454546</v>
       </c>
@@ -9279,7 +9550,7 @@
       <c r="P4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R4" s="5">
@@ -9334,10 +9605,10 @@
         <v>24</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" ref="P5:P49" si="0">(D5-G5)/D5*100</f>
+        <f t="shared" ref="P5" si="0">(D5-G5)/D5*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R5" s="7" t="s">
@@ -9393,8 +9664,8 @@
       <c r="P6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="11">
-        <f t="shared" ref="Q6:Q49" si="1">(D6-H6)/D6*100</f>
+      <c r="Q6" s="3">
+        <f t="shared" ref="Q6" si="1">(D6-H6)/D6*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R6" s="7" t="s">
@@ -9450,11 +9721,11 @@
       <c r="P7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R7" s="7">
-        <f t="shared" ref="R7:R49" si="2">(D7-I7)/D7*100</f>
+        <f t="shared" ref="R7" si="2">(D7-I7)/D7*100</f>
         <v>38.095238095238095</v>
       </c>
     </row>
@@ -9505,10 +9776,10 @@
         <v>23</v>
       </c>
       <c r="P8" s="7">
-        <f t="shared" ref="P8:P49" si="3">(D8-G8)/D8*100</f>
+        <f t="shared" ref="P8" si="3">(D8-G8)/D8*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R8" s="7" t="s">
@@ -9564,8 +9835,8 @@
       <c r="P9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="11">
-        <f t="shared" ref="Q9:Q49" si="4">(D9-H9)/D9*100</f>
+      <c r="Q9" s="3">
+        <f t="shared" ref="Q9" si="4">(D9-H9)/D9*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R9" s="7" t="s">
@@ -9621,11 +9892,11 @@
       <c r="P10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" ref="R10:R49" si="5">(D10-I10)/D10*100</f>
+        <f t="shared" ref="R10" si="5">(D10-I10)/D10*100</f>
         <v>50.887573964497044</v>
       </c>
     </row>
@@ -9676,10 +9947,10 @@
         <v>20</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" ref="P11:P49" si="6">(D11-G11)/D11*100</f>
+        <f t="shared" ref="P11" si="6">(D11-G11)/D11*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R11" s="7" t="s">
@@ -9735,8 +10006,8 @@
       <c r="P12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q12" s="11">
-        <f t="shared" ref="Q12:Q49" si="7">(D12-H12)/D12*100</f>
+      <c r="Q12" s="3">
+        <f t="shared" ref="Q12" si="7">(D12-H12)/D12*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R12" s="7" t="s">
@@ -9792,11 +10063,11 @@
       <c r="P13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" ref="R13:R49" si="8">(D13-I13)/D13*100</f>
+        <f t="shared" ref="R13" si="8">(D13-I13)/D13*100</f>
         <v>44.773175542406314</v>
       </c>
     </row>
@@ -9847,10 +10118,10 @@
         <v>22</v>
       </c>
       <c r="P14" s="7">
-        <f t="shared" ref="P14:P49" si="9">(D14-G14)/D14*100</f>
+        <f t="shared" ref="P14" si="9">(D14-G14)/D14*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R14" s="7" t="s">
@@ -9906,7 +10177,7 @@
       <c r="P15" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="11">
         <f>(D15-H15)/D15*100</f>
         <v>3.2670454545454546</v>
       </c>
@@ -9963,11 +10234,11 @@
       <c r="P16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="Q16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R16" s="7">
-        <f t="shared" ref="R16:R49" si="10">(D16-I16)/D16*100</f>
+        <f t="shared" ref="R16" si="10">(D16-I16)/D16*100</f>
         <v>23.75</v>
       </c>
     </row>
@@ -10018,10 +10289,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" ref="P17:P49" si="11">(D17-G17)/D17*100</f>
+        <f t="shared" ref="P17" si="11">(D17-G17)/D17*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="Q17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R17" s="7" t="s">
@@ -10077,8 +10348,8 @@
       <c r="P18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q18" s="11">
-        <f t="shared" ref="Q18:Q49" si="12">(D18-H18)/D18*100</f>
+      <c r="Q18" s="3">
+        <f t="shared" ref="Q18" si="12">(D18-H18)/D18*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R18" s="7" t="s">
@@ -10134,11 +10405,11 @@
       <c r="P19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="Q19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R19" s="7">
-        <f t="shared" ref="R19:R49" si="13">(D19-I19)/D19*100</f>
+        <f t="shared" ref="R19" si="13">(D19-I19)/D19*100</f>
         <v>37.869822485207102</v>
       </c>
     </row>
@@ -10189,10 +10460,10 @@
         <v>20</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" ref="P20:P49" si="14">(D20-G20)/D20*100</f>
+        <f t="shared" ref="P20" si="14">(D20-G20)/D20*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="Q20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R20" s="7" t="s">
@@ -10248,8 +10519,8 @@
       <c r="P21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q21" s="11">
-        <f t="shared" ref="Q21:Q49" si="15">(D21-H21)/D21*100</f>
+      <c r="Q21" s="3">
+        <f t="shared" ref="Q21" si="15">(D21-H21)/D21*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R21" s="7" t="s">
@@ -10305,11 +10576,11 @@
       <c r="P22" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="11" t="s">
+      <c r="Q22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:R49" si="16">(D22-I22)/D22*100</f>
+        <f t="shared" ref="R22" si="16">(D22-I22)/D22*100</f>
         <v>31.952662721893493</v>
       </c>
     </row>
@@ -10360,10 +10631,10 @@
         <v>24</v>
       </c>
       <c r="P23" s="7">
-        <f t="shared" ref="P23:P49" si="17">(D23-G23)/D23*100</f>
+        <f t="shared" ref="P23" si="17">(D23-G23)/D23*100</f>
         <v>4.4034090909090908</v>
       </c>
-      <c r="Q23" s="11" t="s">
+      <c r="Q23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R23" s="7" t="s">
@@ -10419,8 +10690,8 @@
       <c r="P24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q24" s="11">
-        <f t="shared" ref="Q24:Q49" si="18">(D24-H24)/D24*100</f>
+      <c r="Q24" s="3">
+        <f t="shared" ref="Q24" si="18">(D24-H24)/D24*100</f>
         <v>3.2670454545454546</v>
       </c>
       <c r="R24" s="7" t="s">
@@ -10476,11 +10747,11 @@
       <c r="P25" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="Q25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R25" s="7">
-        <f t="shared" ref="R25:R49" si="19">(D25-I25)/D25*100</f>
+        <f t="shared" ref="R25" si="19">(D25-I25)/D25*100</f>
         <v>14.003944773175542</v>
       </c>
     </row>
@@ -10531,10 +10802,10 @@
         <v>20</v>
       </c>
       <c r="P26" s="7">
-        <f t="shared" ref="P26:P49" si="20">(D26-G26)/D26*100</f>
+        <f t="shared" ref="P26" si="20">(D26-G26)/D26*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="Q26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R26" s="7" t="s">
@@ -10590,8 +10861,8 @@
       <c r="P27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q27" s="11">
-        <f t="shared" ref="Q27:Q49" si="21">(D27-H27)/D27*100</f>
+      <c r="Q27" s="3">
+        <f t="shared" ref="Q27" si="21">(D27-H27)/D27*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R27" s="7" t="s">
@@ -10647,11 +10918,11 @@
       <c r="P28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q28" s="11" t="s">
+      <c r="Q28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" ref="R28:R49" si="22">(D28-I28)/D28*100</f>
+        <f t="shared" ref="R28" si="22">(D28-I28)/D28*100</f>
         <v>24.912280701754387</v>
       </c>
     </row>
@@ -10702,10 +10973,10 @@
         <v>20</v>
       </c>
       <c r="P29" s="7">
-        <f t="shared" ref="P29:P49" si="23">(D29-G29)/D29*100</f>
+        <f t="shared" ref="P29" si="23">(D29-G29)/D29*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q29" s="11" t="s">
+      <c r="Q29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R29" s="7" t="s">
@@ -10761,8 +11032,8 @@
       <c r="P30" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q30" s="11">
-        <f t="shared" ref="Q30:Q49" si="24">(D30-H30)/D30*100</f>
+      <c r="Q30" s="3">
+        <f t="shared" ref="Q30" si="24">(D30-H30)/D30*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R30" s="7" t="s">
@@ -10818,11 +11089,11 @@
       <c r="P31" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q31" s="11" t="s">
+      <c r="Q31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" ref="R31:R49" si="25">(D31-I31)/D31*100</f>
+        <f t="shared" ref="R31" si="25">(D31-I31)/D31*100</f>
         <v>42.807017543859651</v>
       </c>
     </row>
@@ -10873,10 +11144,10 @@
         <v>23</v>
       </c>
       <c r="P32" s="7">
-        <f t="shared" ref="P32:P49" si="26">(D32-G32)/D32*100</f>
+        <f t="shared" ref="P32" si="26">(D32-G32)/D32*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q32" s="11" t="s">
+      <c r="Q32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R32" s="7" t="s">
@@ -10932,8 +11203,8 @@
       <c r="P33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q33" s="11">
-        <f t="shared" ref="Q33:Q49" si="27">(D33-H33)/D33*100</f>
+      <c r="Q33" s="3">
+        <f t="shared" ref="Q33" si="27">(D33-H33)/D33*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R33" s="7" t="s">
@@ -10989,11 +11260,11 @@
       <c r="P34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q34" s="11" t="s">
+      <c r="Q34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" ref="R34:R49" si="28">(D34-I34)/D34*100</f>
+        <f t="shared" ref="R34" si="28">(D34-I34)/D34*100</f>
         <v>63.157894736842103</v>
       </c>
     </row>
@@ -11044,10 +11315,10 @@
         <v>24</v>
       </c>
       <c r="P35" s="7">
-        <f t="shared" ref="P35:P49" si="29">(D35-G35)/D35*100</f>
+        <f t="shared" ref="P35" si="29">(D35-G35)/D35*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q35" s="11" t="s">
+      <c r="Q35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R35" s="7" t="s">
@@ -11103,8 +11374,8 @@
       <c r="P36" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q36" s="11">
-        <f t="shared" ref="Q36:Q49" si="30">(D36-H36)/D36*100</f>
+      <c r="Q36" s="3">
+        <f t="shared" ref="Q36" si="30">(D36-H36)/D36*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R36" s="7" t="s">
@@ -11160,11 +11431,11 @@
       <c r="P37" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q37" s="11" t="s">
+      <c r="Q37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R37" s="7">
-        <f t="shared" ref="R37:R49" si="31">(D37-I37)/D37*100</f>
+        <f t="shared" ref="R37" si="31">(D37-I37)/D37*100</f>
         <v>13.333333333333334</v>
       </c>
     </row>
@@ -11215,10 +11486,10 @@
         <v>22</v>
       </c>
       <c r="P38" s="7">
-        <f t="shared" ref="P38:P49" si="32">(D38-G38)/D38*100</f>
+        <f t="shared" ref="P38" si="32">(D38-G38)/D38*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q38" s="11" t="s">
+      <c r="Q38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R38" s="7" t="s">
@@ -11274,8 +11545,8 @@
       <c r="P39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q39" s="11">
-        <f t="shared" ref="Q39:Q49" si="33">(D39-H39)/D39*100</f>
+      <c r="Q39" s="3">
+        <f t="shared" ref="Q39" si="33">(D39-H39)/D39*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R39" s="7" t="s">
@@ -11331,11 +11602,11 @@
       <c r="P40" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q40" s="11" t="s">
+      <c r="Q40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R40" s="7">
-        <f t="shared" ref="R40:R49" si="34">(D40-I40)/D40*100</f>
+        <f t="shared" ref="R40" si="34">(D40-I40)/D40*100</f>
         <v>21.153846153846153</v>
       </c>
     </row>
@@ -11386,10 +11657,10 @@
         <v>23</v>
       </c>
       <c r="P41" s="7">
-        <f t="shared" ref="P41:P49" si="35">(D41-G41)/D41*100</f>
+        <f t="shared" ref="P41" si="35">(D41-G41)/D41*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q41" s="11" t="s">
+      <c r="Q41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R41" s="7" t="s">
@@ -11445,8 +11716,8 @@
       <c r="P42" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q42" s="11">
-        <f t="shared" ref="Q42:Q49" si="36">(D42-H42)/D42*100</f>
+      <c r="Q42" s="3">
+        <f t="shared" ref="Q42" si="36">(D42-H42)/D42*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R42" s="7" t="s">
@@ -11502,11 +11773,11 @@
       <c r="P43" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q43" s="11" t="s">
+      <c r="Q43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" ref="R43:R49" si="37">(D43-I43)/D43*100</f>
+        <f t="shared" ref="R43" si="37">(D43-I43)/D43*100</f>
         <v>46.315789473684212</v>
       </c>
     </row>
@@ -11557,10 +11828,10 @@
         <v>24</v>
       </c>
       <c r="P44" s="7">
-        <f t="shared" ref="P44:P49" si="38">(D44-G44)/D44*100</f>
+        <f t="shared" ref="P44" si="38">(D44-G44)/D44*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q44" s="11" t="s">
+      <c r="Q44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R44" s="7" t="s">
@@ -11616,8 +11887,8 @@
       <c r="P45" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q45" s="11">
-        <f t="shared" ref="Q45:Q49" si="39">(D45-H45)/D45*100</f>
+      <c r="Q45" s="3">
+        <f t="shared" ref="Q45" si="39">(D45-H45)/D45*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R45" s="7" t="s">
@@ -11673,11 +11944,11 @@
       <c r="P46" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q46" s="11" t="s">
+      <c r="Q46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R46" s="7">
-        <f t="shared" ref="R46:R49" si="40">(D46-I46)/D46*100</f>
+        <f t="shared" ref="R46" si="40">(D46-I46)/D46*100</f>
         <v>33.852140077821012</v>
       </c>
     </row>
@@ -11728,10 +11999,10 @@
         <v>22</v>
       </c>
       <c r="P47" s="7">
-        <f t="shared" ref="P47:P49" si="41">(D47-G47)/D47*100</f>
+        <f t="shared" ref="P47" si="41">(D47-G47)/D47*100</f>
         <v>4.5197740112994351</v>
       </c>
-      <c r="Q47" s="11" t="s">
+      <c r="Q47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R47" s="7" t="s">
@@ -11787,8 +12058,8 @@
       <c r="P48" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q48" s="11">
-        <f t="shared" ref="Q48:Q49" si="42">(D48-H48)/D48*100</f>
+      <c r="Q48" s="3">
+        <f t="shared" ref="Q48" si="42">(D48-H48)/D48*100</f>
         <v>4.4715447154471546</v>
       </c>
       <c r="R48" s="7" t="s">
@@ -11844,7 +12115,7 @@
       <c r="P49" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="11" t="s">
+      <c r="Q49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R49" s="7">
@@ -19012,6 +19283,27 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CCB32F-DE6B-44E3-8238-8DFD8D5AAD6F}">
+  <dimension ref="B20:M21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -19020,7 +19312,7 @@
   <dimension ref="A1:R49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="17" max="17" width="8.7265625" style="15"/>
+    <col min="17" max="17" width="8.7265625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
@@ -19072,7 +19364,7 @@
       <c r="P1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="14"/>
+      <c r="Q1" s="12"/>
       <c r="R1" s="7"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -19088,7 +19380,7 @@
       <c r="D2">
         <v>704</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F2">
@@ -19144,7 +19436,7 @@
       <c r="D3">
         <v>634</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F3">
@@ -19201,7 +19493,7 @@
       <c r="D4">
         <v>704</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F4">
@@ -19257,7 +19549,7 @@
       <c r="D5">
         <v>704</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F5">
@@ -19313,7 +19605,7 @@
       <c r="D6">
         <v>634</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F6">
@@ -19370,7 +19662,7 @@
       <c r="D7">
         <v>704</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F7">
@@ -19426,7 +19718,7 @@
       <c r="D8">
         <v>704</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F8">
@@ -19482,7 +19774,7 @@
       <c r="D9">
         <v>634</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F9">
@@ -19539,7 +19831,7 @@
       <c r="D10">
         <v>704</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F10">
@@ -19595,7 +19887,7 @@
       <c r="D11">
         <v>704</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F11">
@@ -19651,7 +19943,7 @@
       <c r="D12">
         <v>634</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F12">
@@ -19708,7 +20000,7 @@
       <c r="D13">
         <v>704</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F13">
@@ -19764,7 +20056,7 @@
       <c r="D14">
         <v>704</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F14">
@@ -19817,7 +20109,7 @@
       <c r="D15">
         <v>704</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F15">
@@ -19870,7 +20162,7 @@
       <c r="D16">
         <v>704</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F16">
@@ -19926,7 +20218,7 @@
       <c r="D17">
         <v>634</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F17">
@@ -19983,7 +20275,7 @@
       <c r="D18">
         <v>704</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F18">
@@ -20039,7 +20331,7 @@
       <c r="D19">
         <v>704</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F19">
@@ -20095,7 +20387,7 @@
       <c r="D20">
         <v>92</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F20">
@@ -20152,7 +20444,7 @@
       <c r="D21">
         <v>704</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F21">
@@ -20208,7 +20500,7 @@
       <c r="D22">
         <v>704</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F22">
@@ -20264,7 +20556,7 @@
       <c r="D23">
         <v>634</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F23">
@@ -20321,7 +20613,7 @@
       <c r="D24">
         <v>704</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F24">
@@ -20377,7 +20669,7 @@
       <c r="D25">
         <v>177</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F25">
@@ -20433,7 +20725,7 @@
       <c r="D26">
         <v>222</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F26">
@@ -20490,7 +20782,7 @@
       <c r="D27">
         <v>409</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F27">
@@ -20546,7 +20838,7 @@
       <c r="D28">
         <v>177</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F28">
@@ -20602,7 +20894,7 @@
       <c r="D29">
         <v>222</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F29">
@@ -20659,7 +20951,7 @@
       <c r="D30">
         <v>409</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F30">
@@ -20715,7 +21007,7 @@
       <c r="D31">
         <v>177</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F31">
@@ -20771,7 +21063,7 @@
       <c r="D32">
         <v>222</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F32">
@@ -20828,7 +21120,7 @@
       <c r="D33">
         <v>409</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F33">
@@ -20884,7 +21176,7 @@
       <c r="D34">
         <v>177</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F34">
@@ -20940,7 +21232,7 @@
       <c r="D35">
         <v>222</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F35">
@@ -20997,7 +21289,7 @@
       <c r="D36">
         <v>409</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F36">
@@ -21053,7 +21345,7 @@
       <c r="D37">
         <v>177</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F37">
@@ -21109,7 +21401,7 @@
       <c r="D38">
         <v>222</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F38">
@@ -21166,7 +21458,7 @@
       <c r="D39">
         <v>409</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F39">
@@ -21222,7 +21514,7 @@
       <c r="D40">
         <v>177</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F40">
@@ -21278,7 +21570,7 @@
       <c r="D41">
         <v>222</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F41">
@@ -21335,7 +21627,7 @@
       <c r="D42">
         <v>409</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F42">
@@ -21391,7 +21683,7 @@
       <c r="D43">
         <v>177</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F43">
@@ -21447,7 +21739,7 @@
       <c r="D44">
         <v>222</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F44">
@@ -21504,7 +21796,7 @@
       <c r="D45">
         <v>409</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F45">
@@ -21560,7 +21852,7 @@
       <c r="D46">
         <v>177</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F46">
@@ -21616,7 +21908,7 @@
       <c r="D47">
         <v>222</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F47">
@@ -21673,7 +21965,7 @@
       <c r="D48">
         <v>409</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F48">
@@ -21718,7 +22010,7 @@
     </row>
     <row r="49" spans="16:18" x14ac:dyDescent="0.35">
       <c r="P49" s="7"/>
-      <c r="Q49" s="14"/>
+      <c r="Q49" s="12"/>
       <c r="R49" s="7"/>
     </row>
   </sheetData>
@@ -21726,11 +22018,11 @@
   <conditionalFormatting sqref="Q1 Q3 Q49:Q1048576">
     <cfRule type="top10" priority="3" rank="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:Q47">
+    <cfRule type="top10" dxfId="0" priority="1" rank="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Q47 Q44 Q41 Q38 Q35 Q32 Q29 Q26 Q23 Q20 Q17 Q12 Q9 Q6">
     <cfRule type="top10" priority="2" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q47">
-    <cfRule type="top10" dxfId="0" priority="1" rank="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
